--- a/templates_formats/materia pendiente.xlsx
+++ b/templates_formats/materia pendiente.xlsx
@@ -85,15 +85,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,7 +108,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -191,57 +191,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="13"/>
     </xf>
@@ -249,9 +217,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -261,46 +226,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="23"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="30"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="18"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="16"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="19"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -603,14 +557,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
     <col min="2" max="2" width="3.125" customWidth="1"/>
     <col min="3" max="3" width="11.625" customWidth="1"/>
-    <col min="4" max="4" width="34.375" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="4" max="4" width="31.625" customWidth="1"/>
+    <col min="5" max="5" width="18.25" customWidth="1"/>
     <col min="6" max="6" width="2.375" customWidth="1"/>
     <col min="7" max="7" width="8.125" customWidth="1"/>
     <col min="8" max="8" width="2.25" customWidth="1"/>
@@ -624,47 +578,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="26"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D2" s="27" t="s">
+      <c r="A2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="I2" s="2"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D3" s="28" t="s">
+      <c r="A3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="26"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D4" s="29" t="s">
+      <c r="A4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="26"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D5" s="30" t="s">
+      <c r="A5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="G5" s="2"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D6" s="25" t="s">
+      <c r="A6" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="G6" s="2"/>
-      <c r="J6" s="4"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D7" s="5"/>
+      <c r="D7" s="4"/>
       <c r="E7" s="3"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -673,494 +701,328 @@
       <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D8" s="24" t="s">
+      <c r="A8" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D9" s="5"/>
+      <c r="D9" s="4"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="15" t="s">
+      <c r="A10" s="7"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="15" t="s">
+      <c r="G10" s="23"/>
+      <c r="H10" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="11" t="s">
+      <c r="I10" s="23"/>
+      <c r="J10" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="13"/>
-      <c r="L10" s="11" t="s">
+      <c r="K10" s="23"/>
+      <c r="L10" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="11" t="s">
+      <c r="M10" s="23"/>
+      <c r="N10" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="O10" s="13"/>
+      <c r="O10" s="23"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="20" t="s">
         <v>6</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="21" t="s">
         <v>6</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="21" t="s">
         <v>6</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="O11" s="21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="32.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="6">
+    <row r="12" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
         <v>1</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
     </row>
     <row r="13" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>2</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
     </row>
     <row r="14" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>3</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
     </row>
     <row r="15" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>4</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
     </row>
     <row r="16" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>5</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
-    </row>
-    <row r="17" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="6">
+      <c r="C16" s="5"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+    </row>
+    <row r="17" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
         <v>6</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-    </row>
-    <row r="18" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="6">
+      <c r="C17" s="5"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+    </row>
+    <row r="18" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
         <v>7</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-    </row>
-    <row r="19" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="6">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+    </row>
+    <row r="19" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="5">
         <v>8</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-    </row>
-    <row r="20" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="6">
+      <c r="C19" s="5"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+    </row>
+    <row r="20" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="5">
         <v>9</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
-    </row>
-    <row r="21" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="6">
+      <c r="C20" s="5"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+    </row>
+    <row r="21" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="5">
         <v>10</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
-    </row>
-    <row r="22" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="6">
+      <c r="C21" s="5"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+    </row>
+    <row r="22" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="5">
         <v>11</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
-    </row>
-    <row r="23" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
-        <v>12</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-    </row>
-    <row r="24" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="6">
-        <v>13</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18"/>
-      <c r="M24" s="18"/>
-      <c r="N24" s="18"/>
-      <c r="O24" s="18"/>
-    </row>
-    <row r="25" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="6">
-        <v>14</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-    </row>
-    <row r="26" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="6">
-        <v>15</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-    </row>
-    <row r="27" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="6">
-        <v>16</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="18"/>
-      <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
-    </row>
-    <row r="28" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="6">
-        <v>17</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="18"/>
-      <c r="N28" s="18"/>
-      <c r="O28" s="18"/>
-    </row>
-    <row r="29" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="6">
-        <v>18</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-    </row>
-    <row r="30" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="6">
-        <v>19</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-    </row>
-    <row r="31" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9"/>
-      <c r="B31" s="6">
-        <v>20</v>
-      </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-    </row>
-    <row r="33" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="F34" s="2"/>
-    </row>
-    <row r="50" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P50" s="2"/>
-    </row>
-    <row r="51" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P51" s="2"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+    </row>
+    <row r="38" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P39" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A6:O6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="172" orientation="landscape" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
